--- a/outputs/Estadistica Ejercicio/Heatmap/Resumenes_Llamadas/Alteración del orden público.xlsx
+++ b/outputs/Estadistica Ejercicio/Heatmap/Resumenes_Llamadas/Alteración del orden público.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Riña / Pelea Clandestina (Segu" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Persona Agresiva (Seguridad)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Otros Tipos De Alteración Al O" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Alteración Persona Drogada (Se" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Alteración Persona Alcoholizad" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t xml:space="preserve">Municipio</t>
   </si>
@@ -45,18 +47,18 @@
     <t xml:space="preserve">Tula de Allende</t>
   </si>
   <si>
+    <t xml:space="preserve">Tepeapulco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tlahuelilpan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tepeji del Río de Ocampo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zempoala</t>
   </si>
   <si>
-    <t xml:space="preserve">Tlahuelilpan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atotonilco de Tula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actopan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Incidente</t>
   </si>
   <si>
@@ -66,9 +68,15 @@
     <t xml:space="preserve">Persona Agresiva (Seguridad)</t>
   </si>
   <si>
+    <t xml:space="preserve">Alteración Del Orden Público Por Persona Alcoholizada (Seguridad)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Riña / Pelea Clandestina (Seguridad)</t>
   </si>
   <si>
+    <t xml:space="preserve">Alteración Del Orden Público Por Persona Drogada (Seguridad)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Otros Tipos De Alteración Al Orden Público (Seguridad)</t>
   </si>
   <si>
@@ -78,54 +86,27 @@
     <t xml:space="preserve">Clasificacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Centro Norte (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aviación (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pozo Grande (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro Sur (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obrera (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paseos De La Pradera (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primera Sección (Sección)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Castilla (Fraccionamiento)</t>
+    <t xml:space="preserve">La Providencia Siglo Xxi (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tercera (Sección)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuarta (Sección)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Cristóbal (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad Minera 11 De Julio (Unidad Habitacional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampliación Santa Julia (Colonia)</t>
   </si>
   <si>
     <t xml:space="preserve">Centro (Colonia)</t>
   </si>
   <si>
-    <t xml:space="preserve">La Toscana (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Providencia Siglo Xxi (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tercera (Sección)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuarta (Sección)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Cristóbal (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad Minera 11 De Julio (Unidad Habitacional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampliación Santa Julia (Colonia)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Exhacienda De Coscotitlán (Colonia)</t>
   </si>
   <si>
@@ -135,6 +116,36 @@
     <t xml:space="preserve">San Cayetano El Bordo (Colonia)</t>
   </si>
   <si>
+    <t xml:space="preserve">Lomas Del Pedregal (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 De Julio (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rojo Gómez (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Calvario (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miguel Hidalgo (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noxtongo Primera (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Mateo Primera (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tlaxinacalpan (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tianguistengo (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Cerrito (Colonia)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Héroes De Tizayuca (Fraccionamiento)</t>
   </si>
   <si>
@@ -210,12 +221,6 @@
     <t xml:space="preserve">Santa Maria Tecajete (Pueblo)</t>
   </si>
   <si>
-    <t xml:space="preserve">La Floresta (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efrén Rebolledo (Fraccionamiento)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pri Chacón (Fraccionamiento)</t>
   </si>
   <si>
@@ -225,6 +230,12 @@
     <t xml:space="preserve">La Loma</t>
   </si>
   <si>
+    <t xml:space="preserve">Benito Juárez (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Edén (Colonia)</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Depósito (Colonia)</t>
   </si>
   <si>
@@ -243,24 +254,6 @@
     <t xml:space="preserve">San Alfonso Ii (Fraccionamiento)</t>
   </si>
   <si>
-    <t xml:space="preserve">Chapultepec (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colosio (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Cerrito (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estación (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guzmán Mayer Ii (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad Deportiva (Colonia)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azoyatla (Colonia)</t>
   </si>
   <si>
@@ -282,6 +275,48 @@
     <t xml:space="preserve">Céspedes Reforma (Colonia)</t>
   </si>
   <si>
+    <t xml:space="preserve">Tepeapulco (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irolo (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Haciendas (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Cides (Pueblo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaza Vieja (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Loma (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noxtongo Segunda (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan Otlaxpa (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atengo (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caracol (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Loma (Barrio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Francisco Primera (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Mateo Segunda (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María Quelites (Pueblo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Atempa (Barrio)</t>
   </si>
   <si>
@@ -352,6 +387,81 @@
   </si>
   <si>
     <t xml:space="preserve">Villa Margarita (Pueblo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Ávila Camacho (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parque De Poblamiento (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Candelaria (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bartolomé Tepetates (Pueblo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abecedario (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carros (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colonia Del Trabajo (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidalgo (Zona Industrial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Reyes (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahagún (Parque Industrial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Y Minerales (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salvador Allende (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valle De Guadalupe (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huicalco (Barrio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rojo Gómez (Unidad Habitacional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Malinche (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado (Barrio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tlaquilpan (Barrio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Tulipanes (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tadeo De Niza (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacienda De Guadalupe (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Segunda Sección (Barrio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adolfo López Mateos (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan (Colonia)</t>
   </si>
 </sst>
 </file>
@@ -699,7 +809,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>16.8358</v>
+        <v>23.9175</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +820,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>11.4624</v>
+        <v>15.2011</v>
       </c>
     </row>
     <row r="4">
@@ -721,7 +831,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>9.5445</v>
+        <v>13.8505</v>
       </c>
     </row>
     <row r="5">
@@ -732,7 +842,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.2352</v>
+        <v>9.7622</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +853,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>6.6894</v>
+        <v>9.4347</v>
       </c>
     </row>
     <row r="7">
@@ -754,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>6.2688</v>
+        <v>8.1252</v>
       </c>
     </row>
     <row r="8">
@@ -765,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9789</v>
+        <v>7.7621</v>
       </c>
     </row>
     <row r="9">
@@ -776,7 +886,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8108</v>
+        <v>7.6867</v>
       </c>
     </row>
     <row r="10">
@@ -787,7 +897,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7539</v>
+        <v>7.5985</v>
       </c>
     </row>
   </sheetData>
@@ -814,101 +924,101 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>235</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>283</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1759</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>471</v>
+        <v>989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>94</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11">
@@ -916,196 +1026,394 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>3998</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>989</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>305</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>955</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>399</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>574</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>955</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>1131</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>407</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C26" t="n">
-        <v>284</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
       </c>
       <c r="C28" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1125,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1139,359 +1447,359 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
         <v>16</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="n">
         <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1499,16 +1807,16 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
@@ -1516,16 +1824,16 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -1533,16 +1841,16 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
@@ -1550,33 +1858,33 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1584,16 +1892,16 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -1601,16 +1909,16 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -1618,16 +1926,16 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1635,13 +1943,13 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
@@ -1649,19 +1957,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1669,16 +1977,16 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -1686,16 +1994,16 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1703,16 +2011,16 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1720,16 +2028,16 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1737,13 +2045,13 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
         <v>7</v>
@@ -1751,19 +2059,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1771,16 +2079,16 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
@@ -1788,16 +2096,16 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
@@ -1805,16 +2113,16 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -1822,13 +2130,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
         <v>12</v>
@@ -1836,67 +2144,67 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" t="n">
         <v>9</v>
-      </c>
-      <c r="B44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E46" t="n">
         <v>4</v>
@@ -1904,33 +2212,33 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
@@ -1938,16 +2246,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C49" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -1955,18 +2263,35 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1986,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -2000,10 +2325,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2012,12 +2337,12 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -2029,15 +2354,15 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -2046,15 +2371,15 @@
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -2063,15 +2388,15 @@
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -2080,15 +2405,15 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -2097,15 +2422,15 @@
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>170</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -2114,15 +2439,15 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -2131,15 +2456,15 @@
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -2148,15 +2473,15 @@
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -2165,15 +2490,15 @@
         <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -2182,15 +2507,15 @@
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>179</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -2199,15 +2524,15 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -2216,15 +2541,15 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -2233,15 +2558,15 @@
         <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -2250,15 +2575,15 @@
         <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -2267,15 +2592,15 @@
         <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>315</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -2284,15 +2609,15 @@
         <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>190</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -2301,15 +2626,15 @@
         <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>188</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -2318,15 +2643,15 @@
         <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -2335,7 +2660,7 @@
         <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -2343,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -2360,7 +2685,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -2377,7 +2702,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -2411,7 +2736,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -2428,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -2445,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -2462,7 +2787,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -2496,7 +2821,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -2530,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -2547,7 +2872,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -2564,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -2581,7 +2906,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -2598,7 +2923,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -2615,7 +2940,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -2632,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -2649,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -2666,7 +2991,7 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -2680,10 +3005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -2697,10 +3022,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
@@ -2714,10 +3039,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
@@ -2731,10 +3056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
@@ -2748,10 +3073,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
@@ -2779,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -2793,194 +3118,194 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
@@ -2989,15 +3314,15 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
         <v>29</v>
@@ -3006,185 +3331,185 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -3193,180 +3518,1602 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
         <v>7</v>
       </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" t="s">
+        <v>113</v>
+      </c>
+      <c r="C71" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>63</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="s">
+        <v>119</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="s">
+        <v>121</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>122</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3374,16 +5121,16 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -3391,16 +5138,16 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -3408,101 +5155,101 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3510,16 +5257,16 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -3527,16 +5274,16 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -3544,16 +5291,16 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -3561,33 +5308,33 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="n">
         <v>6</v>
-      </c>
-      <c r="B48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -3595,16 +5342,16 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -3612,16 +5359,16 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
@@ -3629,16 +5376,16 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -3646,16 +5393,16 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C52" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3663,47 +5410,47 @@
         <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -3711,325 +5458,1033 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C57" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="C59" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C60" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>121</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
         <v>59</v>
       </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
         <v>60</v>
       </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68" t="s">
-        <v>105</v>
-      </c>
-      <c r="C68" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69" t="s">
-        <v>106</v>
-      </c>
-      <c r="C69" t="s">
-        <v>4</v>
-      </c>
-      <c r="D69" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70" t="s">
-        <v>107</v>
-      </c>
-      <c r="C70" t="s">
-        <v>4</v>
-      </c>
-      <c r="D70" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B71" t="s">
-        <v>108</v>
-      </c>
-      <c r="C71" t="s">
-        <v>4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" t="s">
-        <v>4</v>
-      </c>
-      <c r="D72" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" t="s">
-        <v>4</v>
-      </c>
-      <c r="D73" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" t="s">
-        <v>111</v>
-      </c>
-      <c r="C74" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
